--- a/results/trace_final20_temp06_seed42_pcgrpo-qwen25vl7b-jigsaw-care_20260714T182351Z_results.xlsx
+++ b/results/trace_final20_temp06_seed42_pcgrpo-qwen25vl7b-jigsaw-care_20260714T182351Z_results.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20.2054794520548</v>
+        <v>23.45890410958904</v>
       </c>
       <c r="F9" t="n">
         <v>1168</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>20.2054794520548</v>
+        <v>23.45890410958904</v>
       </c>
       <c r="I9" t="n">
         <v>1168</v>
